--- a/docs/sprint3/execution-log.xlsx
+++ b/docs/sprint3/execution-log.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Environment" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="120">
   <si>
     <t xml:space="preserve">Параметри тестового середовища — Спринт 3</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Дата збірки/перевірки demo</t>
   </si>
   <si>
-    <t xml:space="preserve">26.10.2026</t>
+    <t xml:space="preserve">28.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Версія / стан demo</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">Основний браузер</t>
   </si>
   <si>
-    <t xml:space="preserve">Firefox</t>
+    <t xml:space="preserve">Google Chrome</t>
   </si>
   <si>
     <t xml:space="preserve">Версія браузера</t>
   </si>
   <si>
-    <t xml:space="preserve">Mozilla Firefox 155.0</t>
+    <t xml:space="preserve">Version 153.0.8010.52 (Official Build) (x86_64)</t>
   </si>
   <si>
     <t xml:space="preserve">Резервний браузер</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">TestPass123!</t>
   </si>
   <si>
-    <t xml:space="preserve">107139 ($425.50), 107805 ($90.00)</t>
+    <t xml:space="preserve">13899 ($410.00), 14121 ($90.00)</t>
   </si>
   <si>
     <t xml:space="preserve">Запасний тестовий клієнт</t>
@@ -160,22 +160,220 @@
     <t xml:space="preserve">Коментар / фактичний результат</t>
   </si>
   <si>
+    <t xml:space="preserve">TC-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пономаренко Р.В.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://parabank.parasoft.com/parabank, Chrome 153, Nobara 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поля паролів не зберігаються</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 00:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Банк дозволив операцію</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Банк схвалив кредит</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Після виходу система показує помилку An internal error has occurred and has been logged замість перенаправлення на головну сторінку.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 01:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 02:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Причина: demo відхиляє заявку через внутрішній скоринг (insufficient funds for down payment) незалежно від балансу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/26 02:07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Довідка щодо статусів:</t>
   </si>
   <si>
-    <t xml:space="preserve">passed</t>
-  </si>
-  <si>
     <t xml:space="preserve">Усі очікувані результати збіглися з фактичними</t>
   </si>
   <si>
-    <t xml:space="preserve">failed</t>
-  </si>
-  <si>
     <t xml:space="preserve">Хоча б один крок дав інший результат → обов'язково вказати Bug ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blocked</t>
   </si>
   <si>
     <t xml:space="preserve">Кейс неможливо виконати через інший дефект (вказати Bug ID) або недоступність середовища</t>
@@ -194,7 +392,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,37 +417,23 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <sz val="14"/>
+      <color rgb="FF1B365D"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF1B365D"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -257,27 +441,59 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color rgb="FF1B365D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF375623"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC65911"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFB25900"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,42 +502,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
-        <bgColor rgb="FF1F3864"/>
+        <fgColor rgb="FF1B365D"/>
+        <bgColor rgb="FF333399"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFACD"/>
+        <bgColor rgb="FFF4F7FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF2F5496"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDCE6F1"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <fgColor rgb="FFF4F7FA"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFACD"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -331,29 +553,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -383,73 +592,85 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -465,7 +686,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -477,16 +698,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFACD"/>
-      <rgbColor rgb="FFDCE6F1"/>
+      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFF4F7FA"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -496,29 +717,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF4472C4"/>
+      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FFC65911"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF1B365D"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFB25900"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF2F5496"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF375623"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -704,219 +925,205 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D18" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -934,379 +1141,716 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="50.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+    <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="n">
+      <c r="B3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="B4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="n">
+      <c r="B5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="B6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="n">
+      <c r="B7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
+      <c r="B8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="n">
+      <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="n">
+      <c r="B10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="n">
+      <c r="B11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+      <c r="B12" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="n">
+      <c r="B13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
+      <c r="B14" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="n">
+      <c r="B15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="n">
+      <c r="B16" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
+      <c r="B17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="n">
+      <c r="B18" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="n">
+      <c r="B19" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="n">
+      <c r="B20" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="n">
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-    </row>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B22" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B27:H27"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/sprint3/execution-log.xlsx
+++ b/docs/sprint3/execution-log.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="121">
   <si>
     <t xml:space="preserve">Параметри тестового середовища — Спринт 3</t>
   </si>
@@ -187,7 +187,13 @@
     <t xml:space="preserve">28/10/26 00:27</t>
   </si>
   <si>
-    <t xml:space="preserve">Поля паролів не зберігаються</t>
+    <t xml:space="preserve">failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-006, BUG-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поля паролів не зберігаються, також проблеми з відображенням кирилиці</t>
   </si>
   <si>
     <t xml:space="preserve">TC-004</t>
@@ -238,9 +244,6 @@
     <t xml:space="preserve">28/10/26 01:15</t>
   </si>
   <si>
-    <t xml:space="preserve">failed</t>
-  </si>
-  <si>
     <t xml:space="preserve">BUG-001</t>
   </si>
   <si>
@@ -358,7 +361,10 @@
     <t xml:space="preserve">blocked</t>
   </si>
   <si>
-    <t xml:space="preserve">Причина: demo відхиляє заявку через внутрішній скоринг (insufficient funds for down payment) незалежно від балансу</t>
+    <t xml:space="preserve">система повертає «insufficient funds for down payment» через внутрішній скоринг demo — 
+це стороннє обмеження, не пов'язане з перевіркою межі суми; 
+виконати кейс і порівняти результат з очікуваним неможливо
+Свідомо не ставлю тут статус failed, адже результат тесту не є багом, на мій погляд. Це саме обмеження ресурсу, тому такий статус підходить тут значно краще</t>
   </si>
   <si>
     <t xml:space="preserve">TC-027</t>
@@ -592,84 +598,88 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -928,195 +938,195 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1144,708 +1154,711 @@
   <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="8"/>
+      <c r="D3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="D4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="8" t="s">
+      <c r="D5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>54</v>
       </c>
+      <c r="G5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="12"/>
+      <c r="B6" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="12"/>
+      <c r="B8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="8"/>
+      <c r="B9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="12"/>
+      <c r="B10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="13" t="s">
+      <c r="B13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="C13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="D13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>73</v>
       </c>
+      <c r="H13" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="14" t="s">
+      <c r="C15" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>73</v>
+      <c r="D15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="12"/>
+      <c r="C16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="8"/>
+      <c r="C17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="12"/>
+      <c r="C18" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="B19" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="8"/>
+      <c r="C19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="12"/>
+      <c r="C20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="8"/>
+      <c r="C21" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="15" t="s">
+      <c r="C22" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="D22" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="16" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="H22" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="48.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="B23" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="14" t="s">
+      <c r="C23" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="D23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>99</v>
       </c>
+      <c r="H23" s="9" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="12"/>
+      <c r="C24" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="B25" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="8"/>
+      <c r="C25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B26" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="12"/>
+      <c r="C26" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="6" t="s">
+      <c r="B27" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="n">
+      <c r="C27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="99.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="B28" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="16" t="s">
+      <c r="C28" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="12" t="s">
+      <c r="D28" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
+      <c r="G28" s="11"/>
+      <c r="H28" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="8" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>117</v>
+      <c r="B34" s="19" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" s="18" t="s">
+      <c r="A35" s="20" t="s">
         <v>119</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
